--- a/tests/testdata/TestCaseTemplate.xlsx
+++ b/tests/testdata/TestCaseTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paupau/Desktop/Coding-Projects/Portfolio/Playwright/Use_TypeScript/tests/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381D6B00-860E-CB49-BB6F-55D3C4F5DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1693A5-1139-314E-92A8-A7E30CB7CB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="740" windowWidth="28040" windowHeight="17260" xr2:uid="{5ABECB97-703F-484C-A426-ED4C7928EF9F}"/>
+    <workbookView xWindow="43060" yWindow="8700" windowWidth="38640" windowHeight="17260" xr2:uid="{5ABECB97-703F-484C-A426-ED4C7928EF9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>LocatorValue</t>
   </si>
@@ -56,6 +56,18 @@
   </si>
   <si>
     <t>https://www.google.com</t>
+  </si>
+  <si>
+    <t>waitforURL</t>
+  </si>
+  <si>
+    <t>closeBrowser</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>step</t>
   </si>
 </sst>
 </file>
@@ -418,45 +430,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B27DF450-2CDF-0141-A00E-22509390C165}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{895918BD-EC55-C64A-8DA0-3B5095A6EDB2}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{895918BD-EC55-C64A-8DA0-3B5095A6EDB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/tests/testdata/TestCaseTemplate.xlsx
+++ b/tests/testdata/TestCaseTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paupau/Desktop/Coding-Projects/Portfolio/Playwright/Use_TypeScript/tests/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1693A5-1139-314E-92A8-A7E30CB7CB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB360352-4D90-114F-B98B-241BBF5942DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43060" yWindow="8700" windowWidth="38640" windowHeight="17260" xr2:uid="{5ABECB97-703F-484C-A426-ED4C7928EF9F}"/>
   </bookViews>
